--- a/sample_statements/ICICI_Rohit_2026.xlsx
+++ b/sample_statements/ICICI_Rohit_2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Profile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Account Details" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Account Holder</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -456,12 +456,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Account No</t>
+          <t>Account Number</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>62481000998877</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bengaluru Main Branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Statement Type</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Official Statement</t>
         </is>
       </c>
     </row>
@@ -476,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,17 +542,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>890</v>
+        <v>849.95</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>84110</v>
+        <v>63150.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08-01-2026</t>
+          <t>09-01-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,17 +561,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>69110</v>
+        <v>48600.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11-01-2026</t>
+          <t>13-01-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,17 +580,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3000</v>
+        <v>2955</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>66110</v>
+        <v>45645.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14-01-2026</t>
+          <t>17-01-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -579,13 +603,13 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>65470</v>
+        <v>45005.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17-01-2026</t>
+          <t>21-01-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -594,17 +618,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>999</v>
+        <v>1013.98</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>64471</v>
+        <v>43991.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20-01-2026</t>
+          <t>25-01-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,17 +637,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>890</v>
+        <v>916.7</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>63581</v>
+        <v>43074.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-01-2026</t>
+          <t>29-01-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -632,17 +656,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15000</v>
+        <v>15675</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>48581</v>
+        <v>27399.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26-01-2026</t>
+          <t>02-02-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,17 +675,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3000</v>
+        <v>2865</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>45581</v>
+        <v>24534.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29-01-2026</t>
+          <t>06-02-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,17 +694,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>640</v>
+        <v>620.8</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>44941</v>
+        <v>23913.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01-02-2026</t>
+          <t>10-02-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -689,17 +713,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>999</v>
+        <v>984.01</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>43942</v>
+        <v>22929.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04-02-2026</t>
+          <t>14-02-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -712,13 +736,13 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>43052</v>
+        <v>22039.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07-02-2026</t>
+          <t>18-02-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -727,17 +751,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15000</v>
+        <v>15225</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>28052</v>
+        <v>6814.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10-02-2026</t>
+          <t>22-02-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -746,17 +770,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3000</v>
+        <v>3090</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>25052</v>
+        <v>3724.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13-02-2026</t>
+          <t>26-02-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -765,17 +789,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>640</v>
+        <v>668.8</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>24412</v>
+        <v>3055.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16-02-2026</t>
+          <t>02-03-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -784,17 +808,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>999</v>
+        <v>954.04</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>23413</v>
+        <v>2101.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19-02-2026</t>
+          <t>06-03-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -803,17 +827,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>890</v>
+        <v>863.3</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>22523</v>
+        <v>1238.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22-02-2026</t>
+          <t>10-03-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -822,17 +846,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15000</v>
+        <v>14775</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>7523</v>
+        <v>-13536.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25-02-2026</t>
+          <t>14-03-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -845,13 +869,13 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>4523</v>
+        <v>-16536.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28-02-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -860,17 +884,17 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>640</v>
+        <v>649.6</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>3883</v>
+        <v>-17186.18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03-03-2026</t>
+          <t>22-03-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -879,144 +903,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>999</v>
+        <v>1028.97</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>2884</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>06-03-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>UPI/BLINKIT/77</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>890</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HOUSE RENT UPI LANDLORD</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>-13006</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12-03-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>GROWW SIP MUTUAL FUND</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>-16006</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>UPI/APOLLO PHARMACY/4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>640</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>-16646</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>18-03-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>UPI/JIO FIBER/91</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>999</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>-17645</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>21-03-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>UPI/BLINKIT/77</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>890</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>-18535</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>24-03-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>HOUSE RENT UPI LANDLORD</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="n">
-        <v>-33535</v>
+        <v>-18215.15</v>
       </c>
     </row>
   </sheetData>
